--- a/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>TMHC</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7417800</v>
+      </c>
+      <c r="E8" s="3">
         <v>8224900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7501300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6129300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4762100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4227400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3885300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3550000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2976800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2708400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1916100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1435700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1370200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5623000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6132600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5953400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5085100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3928600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3489200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3146400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2869800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2408900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2142200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1500200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1124700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1090500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1794900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2092400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1547900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1044200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>833500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>738200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>738900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>680300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>567900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>566200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>415900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>311000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>279700</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-13900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>137400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>50900</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>33300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>10100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6832200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6638200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5805200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4439800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3953900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3529600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3235800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2715800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2406400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1911500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1265200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1268500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1017800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1392700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>863100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>324100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>322300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>273500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>355700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>314200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>261000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>302000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>170600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>101700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1178,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1187,51 +1220,57 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1051200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1426500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>903100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>361500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>353700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>299900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>359600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>318200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>265100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>306100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>105900</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1017800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1392700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>863100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>324100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>322300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>273500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>355700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>314200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>261000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>302000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>170600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>101700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E24" s="3">
         <v>336400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>180700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>74600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>67400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>63000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>240000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>107600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>90000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>76400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-23800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-260300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>769700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1056200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>682400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>249500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>254900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>210500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>115700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>206600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>171000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>225600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>430800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>76800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1052800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>663000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>243400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>254700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>206400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>52600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>60200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>29900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>430800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>71500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1538,36 +1598,39 @@
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>61000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>15700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>11300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>15500</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1715,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1691,51 +1760,57 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1052800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>663000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>243400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>254700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>206400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>91200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>52600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>61000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>71500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>45400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>430800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1052800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>663000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>243400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>254700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>206400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>91200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>52600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>61000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>71500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>45400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>430800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>798600</v>
+      </c>
+      <c r="E41" s="3">
         <v>724500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>832800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>532800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>326400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>329600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>573900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>300200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>126200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>234200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>300600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>279300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,135 +2073,147 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>184500</v>
+      </c>
+      <c r="E43" s="3">
         <v>191500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>150900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>96200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>70400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>94500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>115200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>241500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>85300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>50600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97900</v>
       </c>
-      <c r="O43" s="3" t="s">
+      <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5545400</v>
+      </c>
+      <c r="E44" s="3">
         <v>5370900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5499500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5332400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3986500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3980600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2959200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3017200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3126800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2518300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2012600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3210200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1003500</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E45" s="3">
         <v>60300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>102800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>174200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>69900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>59400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>156600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>75700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>168000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,93 +2253,102 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>549400</v>
+      </c>
+      <c r="E47" s="3">
         <v>546300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>400900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>253600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>168600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>198500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>242100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>195100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>162600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>144800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>98100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>308400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>317000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>370300</v>
+      </c>
+      <c r="E48" s="3">
         <v>292800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>241000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>171100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>122500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>86700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2252,35 +2362,38 @@
         <v>663200</v>
       </c>
       <c r="G49" s="3">
+        <v>663200</v>
+      </c>
+      <c r="H49" s="3">
         <v>150100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>153200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>68300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>66200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>46400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9700</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E52" s="3">
         <v>416200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>622300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>440500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>333500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>329200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>306800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>441500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>436500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1027100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1005300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>373400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8672100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8470700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8727800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7738000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5245700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5264400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4325900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4220900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4117400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4133100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3438600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2738100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1671100</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,50 +2654,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>263500</v>
+      </c>
+      <c r="E57" s="3">
         <v>269800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>253300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>215000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>164600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>151600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>140200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>136600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>151900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>122500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>98600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64800</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2594,65 +2727,71 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>109900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>40000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>50000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>949400</v>
+        <v>889800</v>
       </c>
       <c r="E59" s="3">
+        <v>925000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1057300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>798500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>518100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>432100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>338600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>331300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>321600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>321100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>259600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>620400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>373900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,51 +2831,57 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2483900</v>
+        <v>2041400</v>
       </c>
       <c r="E61" s="3">
+        <v>2508200</v>
+      </c>
+      <c r="F61" s="3">
         <v>3302100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2928400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1940800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2209600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1498100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1586500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1553400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1697100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1257700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>977900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>599800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2774,11 +2919,14 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>4000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3357100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3840400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4801900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4233500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2708000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2849200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2729800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3669100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3597500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3654700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3022700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1541400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1051900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3510500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2741600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1688800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1025800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>782400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>527700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>319800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>228600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>176000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>114900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1231000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>649200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5314900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4630300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3925900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3504500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2537700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2415200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1596100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>551800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>519900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>478400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>415800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1196700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>619100</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1052800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>663000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>243400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>254700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>206400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>91200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>52600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>61000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>71500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>45400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>430800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E83" s="3">
         <v>33800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4000</v>
       </c>
       <c r="J83" s="3">
         <v>4000</v>
       </c>
       <c r="K83" s="3">
-        <v>4100</v>
+        <v>4000</v>
       </c>
       <c r="L83" s="3">
         <v>4100</v>
       </c>
       <c r="M83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N83" s="3">
         <v>3500</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>806200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1107800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>376600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1123300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>393200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>135600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>386200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>372600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-262700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-133700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-151900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-214500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>158400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2800</v>
       </c>
       <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-74300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-312800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-159700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-81400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>50200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-89500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-75800</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,8 +4220,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4029,9 +4262,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-628500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1202600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-604900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-377200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-219500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-76500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-103000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>309300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>337900</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-29300</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4225,63 +4473,69 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-20500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21600</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-109700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>302200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>205500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-243600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>273700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>174000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-336000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>73000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>88600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>21200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>113900</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>TMHC</t>
   </si>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5623000</v>
+        <v>5529000</v>
       </c>
       <c r="E9" s="3">
-        <v>6132600</v>
+        <v>6023700</v>
       </c>
       <c r="F9" s="3">
-        <v>5953400</v>
+        <v>5851500</v>
       </c>
       <c r="G9" s="3">
-        <v>5085100</v>
+        <v>4986600</v>
       </c>
       <c r="H9" s="3">
-        <v>3928600</v>
+        <v>3843800</v>
       </c>
       <c r="I9" s="3">
-        <v>3489200</v>
+        <v>3398800</v>
       </c>
       <c r="J9" s="3">
-        <v>3146400</v>
+        <v>3104700</v>
       </c>
       <c r="K9" s="3">
         <v>2869800</v>
@@ -816,22 +816,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1794900</v>
+        <v>1804000</v>
       </c>
       <c r="E10" s="3">
-        <v>2092400</v>
+        <v>2122500</v>
       </c>
       <c r="F10" s="3">
-        <v>1547900</v>
+        <v>1556500</v>
       </c>
       <c r="G10" s="3">
-        <v>1044200</v>
+        <v>1064300</v>
       </c>
       <c r="H10" s="3">
-        <v>833500</v>
+        <v>867200</v>
       </c>
       <c r="I10" s="3">
-        <v>738200</v>
+        <v>787100</v>
       </c>
       <c r="J10" s="3">
         <v>738900</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>81000</v>
+        <v>59700</v>
       </c>
       <c r="E14" s="3">
-        <v>-13900</v>
+        <v>-8300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-9600</v>
       </c>
       <c r="G14" s="3">
-        <v>137400</v>
+        <v>19900</v>
       </c>
       <c r="H14" s="3">
-        <v>25900</v>
+        <v>59600</v>
       </c>
       <c r="I14" s="3">
-        <v>50900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>99800</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9000</v>
+        <v>33400</v>
       </c>
       <c r="E15" s="3">
-        <v>7600</v>
+        <v>33800</v>
       </c>
       <c r="F15" s="3">
-        <v>7500</v>
+        <v>40000</v>
       </c>
       <c r="G15" s="3">
-        <v>6300</v>
+        <v>37300</v>
       </c>
       <c r="H15" s="3">
-        <v>5300</v>
+        <v>31400</v>
       </c>
       <c r="I15" s="3">
-        <v>5000</v>
+        <v>26400</v>
       </c>
       <c r="J15" s="3">
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="K15" s="3">
         <v>2900</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6400000</v>
+        <v>6352500</v>
       </c>
       <c r="E17" s="3">
-        <v>6832200</v>
+        <v>6803400</v>
       </c>
       <c r="F17" s="3">
-        <v>6638200</v>
+        <v>6646500</v>
       </c>
       <c r="G17" s="3">
-        <v>5805200</v>
+        <v>5637400</v>
       </c>
       <c r="H17" s="3">
-        <v>4439800</v>
+        <v>4385100</v>
       </c>
       <c r="I17" s="3">
-        <v>3953900</v>
+        <v>3857200</v>
       </c>
       <c r="J17" s="3">
-        <v>3529600</v>
+        <v>3536800</v>
       </c>
       <c r="K17" s="3">
         <v>3235800</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1017800</v>
+        <v>1065300</v>
       </c>
       <c r="E18" s="3">
-        <v>1392700</v>
+        <v>1421500</v>
       </c>
       <c r="F18" s="3">
-        <v>863100</v>
+        <v>854800</v>
       </c>
       <c r="G18" s="3">
-        <v>324100</v>
+        <v>491900</v>
       </c>
       <c r="H18" s="3">
-        <v>322300</v>
+        <v>376900</v>
       </c>
       <c r="I18" s="3">
-        <v>273500</v>
+        <v>370200</v>
       </c>
       <c r="J18" s="3">
-        <v>355700</v>
+        <v>348500</v>
       </c>
       <c r="K18" s="3">
         <v>314200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>149600</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-2300</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1051200</v>
+        <v>1098300</v>
       </c>
       <c r="E21" s="3">
-        <v>1426500</v>
+        <v>1435900</v>
       </c>
       <c r="F21" s="3">
-        <v>903100</v>
+        <v>897300</v>
       </c>
       <c r="G21" s="3">
-        <v>361500</v>
+        <v>379700</v>
       </c>
       <c r="H21" s="3">
-        <v>353700</v>
+        <v>410600</v>
       </c>
       <c r="I21" s="3">
-        <v>299900</v>
+        <v>398100</v>
       </c>
       <c r="J21" s="3">
-        <v>359600</v>
+        <v>359000</v>
       </c>
       <c r="K21" s="3">
         <v>318200</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>17700</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>3800</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>63000</v>
       </c>
       <c r="J24" s="3">
-        <v>240000</v>
+        <v>179000</v>
       </c>
       <c r="K24" s="3">
         <v>107600</v>
@@ -1473,7 +1473,7 @@
         <v>210500</v>
       </c>
       <c r="J26" s="3">
-        <v>115700</v>
+        <v>176700</v>
       </c>
       <c r="K26" s="3">
         <v>206600</v>
@@ -1518,7 +1518,7 @@
         <v>206400</v>
       </c>
       <c r="J27" s="3">
-        <v>30200</v>
+        <v>91200</v>
       </c>
       <c r="K27" s="3">
         <v>52600</v>
@@ -1601,14 +1601,14 @@
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>61000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-19500</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-149600</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2044,19 +2044,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>41300</v>
+        <v>348600</v>
       </c>
       <c r="E45" s="3">
-        <v>60300</v>
+        <v>328600</v>
       </c>
       <c r="F45" s="3">
-        <v>102800</v>
+        <v>385700</v>
       </c>
       <c r="G45" s="3">
-        <v>174200</v>
+        <v>249500</v>
       </c>
       <c r="H45" s="3">
-        <v>48700</v>
+        <v>43800</v>
       </c>
       <c r="I45" s="3">
-        <v>69900</v>
+        <v>57900</v>
       </c>
       <c r="J45" s="3">
-        <v>53400</v>
+        <v>49800</v>
       </c>
       <c r="K45" s="3">
         <v>59400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>7117200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>7005500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>7380400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>6467500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>4669300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>4707900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3919100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>549400</v>
+        <v>346200</v>
       </c>
       <c r="E47" s="3">
-        <v>546300</v>
+        <v>282900</v>
       </c>
       <c r="F47" s="3">
-        <v>400900</v>
+        <v>171400</v>
       </c>
       <c r="G47" s="3">
-        <v>253600</v>
+        <v>128000</v>
       </c>
       <c r="H47" s="3">
-        <v>168600</v>
+        <v>128800</v>
       </c>
       <c r="I47" s="3">
-        <v>198500</v>
+        <v>140500</v>
       </c>
       <c r="J47" s="3">
-        <v>242100</v>
+        <v>192400</v>
       </c>
       <c r="K47" s="3">
         <v>195100</v>
@@ -2365,7 +2365,7 @@
         <v>663200</v>
       </c>
       <c r="H49" s="3">
-        <v>150100</v>
+        <v>149400</v>
       </c>
       <c r="I49" s="3">
         <v>153200</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>269700</v>
+        <v>104200</v>
       </c>
       <c r="E52" s="3">
-        <v>416200</v>
+        <v>154300</v>
       </c>
       <c r="F52" s="3">
-        <v>622300</v>
+        <v>118700</v>
       </c>
       <c r="G52" s="3">
-        <v>440500</v>
+        <v>68500</v>
       </c>
       <c r="H52" s="3">
-        <v>333500</v>
+        <v>33400</v>
       </c>
       <c r="I52" s="3">
-        <v>329200</v>
+        <v>28300</v>
       </c>
       <c r="J52" s="3">
-        <v>306800</v>
+        <v>18900</v>
       </c>
       <c r="K52" s="3">
         <v>441500</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>381900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>306100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>445400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>127300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>123200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>330400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>118800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2750,26 +2750,26 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>889800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>925000</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F59" s="3">
-        <v>1057300</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>798500</v>
+        <v>14700</v>
       </c>
       <c r="H59" s="3">
-        <v>518100</v>
+        <v>3900</v>
       </c>
       <c r="I59" s="3">
-        <v>432100</v>
+        <v>700</v>
       </c>
       <c r="J59" s="3">
-        <v>338600</v>
+        <v>4800</v>
       </c>
       <c r="K59" s="3">
         <v>331300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1148400</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1012900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1174100</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>746300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>596300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>732000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>450200</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2041400</v>
+        <v>1720200</v>
       </c>
       <c r="E61" s="3">
-        <v>2508200</v>
+        <v>2278000</v>
       </c>
       <c r="F61" s="3">
-        <v>3302100</v>
+        <v>2952900</v>
       </c>
       <c r="G61" s="3">
-        <v>2928400</v>
+        <v>2884300</v>
       </c>
       <c r="H61" s="3">
-        <v>1940800</v>
+        <v>1859900</v>
       </c>
       <c r="I61" s="3">
-        <v>2209600</v>
+        <v>1879200</v>
       </c>
       <c r="J61" s="3">
-        <v>1498100</v>
+        <v>1379200</v>
       </c>
       <c r="K61" s="3">
         <v>1586500</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>471300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>629800</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>513600</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>243800</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>234400</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>149900</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3357100</v>
+        <v>3339800</v>
       </c>
       <c r="E66" s="3">
-        <v>3840400</v>
+        <v>3823900</v>
       </c>
       <c r="F66" s="3">
-        <v>4801900</v>
+        <v>4756800</v>
       </c>
       <c r="G66" s="3">
-        <v>4233500</v>
+        <v>4144200</v>
       </c>
       <c r="H66" s="3">
-        <v>2708000</v>
+        <v>2700000</v>
       </c>
       <c r="I66" s="3">
-        <v>2849200</v>
+        <v>2845700</v>
       </c>
       <c r="J66" s="3">
-        <v>2729800</v>
+        <v>1979300</v>
       </c>
       <c r="K66" s="3">
         <v>3669100</v>
@@ -3712,7 +3712,7 @@
         <v>26400</v>
       </c>
       <c r="J83" s="3">
-        <v>4000</v>
+        <v>2900</v>
       </c>
       <c r="K83" s="3">
         <v>4000</v>
@@ -4451,26 +4451,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>TMHC</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8168100</v>
+      </c>
+      <c r="E8" s="3">
         <v>7417800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8224900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7501300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6129300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4762100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4227400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3885300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3550000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2976800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2708400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1916100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1435700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1370200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6045700</v>
+      </c>
+      <c r="E9" s="3">
         <v>5529000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6023700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5851500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4986600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3843800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3398800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3104700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2869800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2408900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2142200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1500200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1124700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1090500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1804000</v>
+        <v>2013800</v>
       </c>
       <c r="E10" s="3">
-        <v>2122500</v>
+        <v>1794900</v>
       </c>
       <c r="F10" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="G10" s="3">
         <v>1556500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1064300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>867200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>787100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>738900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>680300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>567900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>566200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>415900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>311000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>279700</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>59700</v>
+        <v>8300</v>
       </c>
       <c r="E14" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-8300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>19900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>59600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>99800</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>33300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>10100</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E15" s="3">
         <v>33400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>40000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6352500</v>
+        <v>6924800</v>
       </c>
       <c r="E17" s="3">
-        <v>6803400</v>
+        <v>6321700</v>
       </c>
       <c r="F17" s="3">
+        <v>6750900</v>
+      </c>
+      <c r="G17" s="3">
         <v>6646500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5637400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4385100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3857200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3536800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3235800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2715800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2406400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1911500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1265200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1268500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1065300</v>
+        <v>1243400</v>
       </c>
       <c r="E18" s="3">
-        <v>1421500</v>
+        <v>1096200</v>
       </c>
       <c r="F18" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="G18" s="3">
         <v>854800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>491900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>376900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>370200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>348500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>314200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>261000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>302000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>170600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>101700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,35 +1211,36 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>65600</v>
       </c>
       <c r="E20" s="3">
-        <v>19500</v>
+        <v>95900</v>
       </c>
       <c r="F20" s="3">
+        <v>72000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>149600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1223,68 +1256,74 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1098300</v>
+        <v>1219000</v>
       </c>
       <c r="E21" s="3">
+        <v>1033700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1435900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>897300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>379700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>410600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>398100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>359000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>318200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>265100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>306100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>105900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3800</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>8</v>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1156100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1017800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1392700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>863100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>324100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>322300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>273500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>355700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>314200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>261000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>302000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>170600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>101700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>269500</v>
+      </c>
+      <c r="E24" s="3">
         <v>248100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>336400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>180700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>67400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>63000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>179000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>107600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>90000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>76400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-23800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-260300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>886600</v>
+      </c>
+      <c r="E26" s="3">
         <v>769700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1056200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>682400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>249500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>254900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>210500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>176700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>206600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>171000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>225600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>430800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>76800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>883300</v>
+      </c>
+      <c r="E27" s="3">
         <v>768900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1052800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>663000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>243400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>254700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>206400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>91200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>52600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>45400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>430800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>71500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,23 +1674,26 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>15700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>11300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>15500</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,36 +1784,39 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-65600</v>
       </c>
       <c r="E32" s="3">
-        <v>-19500</v>
+        <v>-95900</v>
       </c>
       <c r="F32" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-149600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1763,54 +1832,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>883300</v>
+      </c>
+      <c r="E33" s="3">
         <v>768900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1052800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>663000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>243400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>254700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>206400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>52600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>61000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>71500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>45400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>430800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>71500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>883300</v>
+      </c>
+      <c r="E35" s="3">
         <v>768900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1052800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>663000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>243400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>254700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>206400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>52600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>61000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>71500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>45400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>430800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>71500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>487200</v>
+      </c>
+      <c r="E41" s="3">
         <v>798600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>724500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>832800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>532800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>326400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>329600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>573900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>234200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>279300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2044,23 +2133,23 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2076,171 +2165,183 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>217700</v>
+      </c>
+      <c r="E43" s="3">
         <v>184500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>191500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>150900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>96200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>70400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>86600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>115200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>241500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>85300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>50600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97900</v>
       </c>
-      <c r="P43" s="3" t="s">
+      <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6234100</v>
+      </c>
+      <c r="E44" s="3">
         <v>5545400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5370900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5499500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5332400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3986500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3980600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2959200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3017200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3126800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2518300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2012600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3210200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1003500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>542600</v>
+      </c>
+      <c r="E45" s="3">
         <v>348600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>328600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>385700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>249500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>57900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>49800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>156600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>75700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>168000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7117200</v>
+        <v>7728800</v>
       </c>
       <c r="E46" s="3">
+        <v>7117400</v>
+      </c>
+      <c r="F46" s="3">
         <v>7005500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7380400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6467500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4669300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4707900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3919100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,99 +2357,108 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>439700</v>
+      </c>
+      <c r="E47" s="3">
         <v>346200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>282900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>171400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>128000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>128800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>140500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>192400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>195100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>162600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>144800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>98100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>308400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>317000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300800</v>
+      </c>
+      <c r="E48" s="3">
         <v>370300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>292800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>241000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>171100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>122500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>86700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2365,35 +2475,38 @@
         <v>663200</v>
       </c>
       <c r="H49" s="3">
+        <v>663200</v>
+      </c>
+      <c r="I49" s="3">
         <v>149400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>153200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>68300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>69400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>66200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>28800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>46400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>60100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9700</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E52" s="3">
         <v>104200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>154300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>118700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>33400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>441500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>436500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1027100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1005300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>373400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9297100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8672100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8470700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8727800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7738000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5245700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5264400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4325900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4220900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4117400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4133100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3438600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2738100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1671100</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,170 +2784,180 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>270300</v>
+      </c>
+      <c r="E57" s="3">
         <v>263500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>269800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>253300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>215000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>164600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>151600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>140200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>136600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>151900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>122500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64800</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>381900</v>
+        <v>326800</v>
       </c>
       <c r="E58" s="3">
+        <v>153500</v>
+      </c>
+      <c r="F58" s="3">
         <v>306100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>445400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>127300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>123200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>330400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>118800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>109900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>40000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>50000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>2200</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>331300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>321600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>321100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>259600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>620400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>373900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1148400</v>
+        <v>1187500</v>
       </c>
       <c r="E60" s="3">
+        <v>919900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1012900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1174100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>746300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>596300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>732000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>450200</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2834,81 +2973,87 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1720200</v>
+        <v>1872700</v>
       </c>
       <c r="E61" s="3">
+        <v>1948600</v>
+      </c>
+      <c r="F61" s="3">
         <v>2278000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2952900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2884300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1859900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1879200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1379200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1586500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1553400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1697100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1257700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>977900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>599800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>358800</v>
+      </c>
+      <c r="E62" s="3">
         <v>471300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>533000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>629800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>513600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>243800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>234400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>149900</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2922,11 +3067,14 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3419000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3339800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3823900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4756800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4144200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2700000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2845700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1979300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3669100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3597500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3654700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3022700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1541400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1051900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4393900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3510500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2741600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1688800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1025800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>782400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>527700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>319800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>228600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>176000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>114900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1231000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>649200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5866500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5314900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4630300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3925900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3504500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2537700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2415200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1596100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>551800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>519900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>478400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>415800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1196700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>619100</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>883300</v>
+      </c>
+      <c r="E81" s="3">
         <v>768900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1052800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>663000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>243400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>254700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>206400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>52600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>61000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>71500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>45400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>430800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>71500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E83" s="3">
         <v>33400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4100</v>
       </c>
       <c r="M83" s="3">
         <v>4100</v>
       </c>
       <c r="N83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>210100</v>
+      </c>
+      <c r="E89" s="3">
         <v>806200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1107800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>376600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1123300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>393200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>135600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>386200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>372600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-262700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-133700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-151900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-214500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>158400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-33400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-37800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-2800</v>
       </c>
       <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-136400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-97200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-74300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-312800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-159700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-81400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>50200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-89500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-75800</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-393600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-628500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1202600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-604900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-377200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-219500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-76500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-117300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-103000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>309300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>337900</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-29300</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4472,70 +4720,76 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-20500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21600</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-319900</v>
+      </c>
+      <c r="E102" s="3">
         <v>80500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-109700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>302200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>205500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-243600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>273700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>174000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-336000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>73000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>88600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>113900</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TMHC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>TMHC</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8121500</v>
+      </c>
+      <c r="E8" s="3">
         <v>8168100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7417800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8224900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7501300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6129300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4762100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4227400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3885300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3550000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2976800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2708400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1916100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1435700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1370200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6117800</v>
+      </c>
+      <c r="E9" s="3">
         <v>6045700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5529000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6023700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5851500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4986600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3843800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3398800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3104700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2869800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2408900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2142200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1500200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1124700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1090500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1899000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2013800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1794900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2117200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1556500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1064300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>867200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>787100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>738900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>680300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>567900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>566200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>415900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>311000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>279700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>8300</v>
+        <v>61700</v>
       </c>
       <c r="E14" s="3">
-        <v>-5000</v>
+        <v>74600</v>
       </c>
       <c r="F14" s="3">
-        <v>-8300</v>
+        <v>12100</v>
       </c>
       <c r="G14" s="3">
-        <v>-9600</v>
+        <v>1300</v>
       </c>
       <c r="H14" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I14" s="3">
         <v>19900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>59600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>99800</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>33300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>10100</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E15" s="3">
         <v>41200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>40000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>31400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6957400</v>
+      </c>
+      <c r="E17" s="3">
         <v>6924800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6321700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6750900</v>
       </c>
-      <c r="G17" s="3">
-        <v>6646500</v>
-      </c>
       <c r="H17" s="3">
+        <v>6627300</v>
+      </c>
+      <c r="I17" s="3">
         <v>5637400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4385100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3857200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3536800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3235800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2715800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2406400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1911500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1265200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1268500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1243400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1096200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1474000</v>
       </c>
-      <c r="G18" s="3">
-        <v>854800</v>
-      </c>
       <c r="H18" s="3">
+        <v>874000</v>
+      </c>
+      <c r="I18" s="3">
         <v>491900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>376900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>370200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>348500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>314200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>261000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>302000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>170600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>101700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,38 +1244,39 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>65600</v>
+        <v>13200</v>
       </c>
       <c r="E20" s="3">
-        <v>95900</v>
+        <v>-700</v>
       </c>
       <c r="F20" s="3">
-        <v>72000</v>
+        <v>78800</v>
       </c>
       <c r="G20" s="3">
+        <v>62400</v>
+      </c>
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>149600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1259,74 +1292,80 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1219000</v>
+        <v>1191000</v>
       </c>
       <c r="E21" s="3">
-        <v>1033700</v>
+        <v>1285200</v>
       </c>
       <c r="F21" s="3">
-        <v>1435900</v>
+        <v>1050800</v>
       </c>
       <c r="G21" s="3">
-        <v>897300</v>
+        <v>1445500</v>
       </c>
       <c r="H21" s="3">
+        <v>916500</v>
+      </c>
+      <c r="I21" s="3">
         <v>379700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>410600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>398100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>359000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>318200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>265100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>306100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>105900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13300</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3800</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1042000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1156100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1017800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1392700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>863100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>324100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>322300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>273500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>355700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>314200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>261000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>302000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>170600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>101700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>250800</v>
+      </c>
+      <c r="E24" s="3">
         <v>269500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>248100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>336400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>180700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>74600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>63000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>179000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>107600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>90000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>76400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-23800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-260300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>791300</v>
+      </c>
+      <c r="E26" s="3">
         <v>886600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>769700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1056200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>682400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>249500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>254900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>210500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>176700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>206600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>171000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>225600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>28400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>430800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>76800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>782500</v>
+      </c>
+      <c r="E27" s="3">
         <v>883300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>768900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1052800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>663000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>243400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>254700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>206400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>91200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>52600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>45400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>60200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>430800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>71500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,23 +1737,26 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>15700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>11300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>15500</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,39 +1853,42 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-65600</v>
+        <v>-13200</v>
       </c>
       <c r="E32" s="3">
-        <v>-95900</v>
+        <v>700</v>
       </c>
       <c r="F32" s="3">
-        <v>-72000</v>
+        <v>-78800</v>
       </c>
       <c r="G32" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-149600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1835,57 +1904,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>782500</v>
+      </c>
+      <c r="E33" s="3">
         <v>883300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>768900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1052800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>663000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>243400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>254700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>206400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>91200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>52600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>61000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>71500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>45400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>430800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>71500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>782500</v>
+      </c>
+      <c r="E35" s="3">
         <v>883300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>768900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1052800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>663000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>243400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>254700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>206400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>91200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>52600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>61000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>71500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>45400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>430800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>71500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>850000</v>
+      </c>
+      <c r="E41" s="3">
         <v>487200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>798600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>724500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>832800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>532800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>326400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>329600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>573900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>234200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>193500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>279300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2136,23 +2225,23 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2168,183 +2257,195 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E43" s="3">
         <v>217700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>184500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>191500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>150900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>96200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>70400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>86600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>115200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>241500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>85300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97900</v>
       </c>
-      <c r="Q43" s="3" t="s">
+      <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6140700</v>
+      </c>
+      <c r="E44" s="3">
         <v>6234100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5545400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5370900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5499500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5332400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3986500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3980600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2959200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3017200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3126800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2518300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2012600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3210200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1003500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>654400</v>
+      </c>
+      <c r="E45" s="3">
         <v>542600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>348600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>328600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>385700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>249500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>43800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>156600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>75700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>168000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8088200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7728800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7117400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7005500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7380400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6467500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4669300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4707900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3919100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,105 +2461,114 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E47" s="3">
         <v>439700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>346200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>282900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>171400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>128000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>128800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>140500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>192400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>195100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>162600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>144800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>98100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>308400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>317000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>319800</v>
+      </c>
+      <c r="E48" s="3">
         <v>300800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>370300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>292800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>241000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>171100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>122500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>86700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2478,35 +2588,38 @@
         <v>663200</v>
       </c>
       <c r="I49" s="3">
+        <v>663200</v>
+      </c>
+      <c r="J49" s="3">
         <v>149400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>153200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>68300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>69400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>66200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>46400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>60100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9700</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E52" s="3">
         <v>86400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>104200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>154300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>118700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>68500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>33400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>441500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>436500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1027100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1005300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>373400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9837800</v>
+      </c>
+      <c r="E54" s="3">
         <v>9297100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8672100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8470700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8727800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7738000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5245700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5264400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4325900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4220900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4117400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4133100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3438600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2738100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1671100</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,182 +2914,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>251600</v>
+      </c>
+      <c r="E57" s="3">
         <v>270300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>263500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>269800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>253300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>215000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>164600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>151600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>140200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>136600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>151900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>122500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>98600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>64800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>326800</v>
+        <v>331200</v>
       </c>
       <c r="E58" s="3">
+        <v>174500</v>
+      </c>
+      <c r="F58" s="3">
         <v>153500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>306100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>445400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>123200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>330400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>118800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>109900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>50000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2200</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>331300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>321600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>321100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>259600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>620400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>373900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1187500</v>
+        <v>1196400</v>
       </c>
       <c r="E60" s="3">
+        <v>1035200</v>
+      </c>
+      <c r="F60" s="3">
         <v>919900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1012900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1174100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>746300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>596300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>732000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>450200</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2976,87 +3115,93 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1872700</v>
+        <v>2031400</v>
       </c>
       <c r="E61" s="3">
+        <v>2025000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1948600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2278000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2952900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2884300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1859900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1879200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1379200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1586500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1553400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1697100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1257700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>977900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>599800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300700</v>
+      </c>
+      <c r="E62" s="3">
         <v>358800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>471300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>533000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>629800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>513600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>243800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>234400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>149900</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3070,11 +3215,14 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>4000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3528500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3419000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3339800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3823900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4756800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4144200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2700000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2845700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1979300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3669100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3597500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3654700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3022700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1541400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1051900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5176400</v>
+      </c>
+      <c r="E72" s="3">
         <v>4393900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3510500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2741600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1688800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1025800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>782400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>527700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>319800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>228600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>176000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>114900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>649200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6293300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5866500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5314900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4630300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3925900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3504500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2537700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2415200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1596100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>551800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>519900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>478400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>415800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1196700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>619100</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>782500</v>
+      </c>
+      <c r="E81" s="3">
         <v>883300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>768900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1052800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>663000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>243400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>254700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>206400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>91200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>52600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>61000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>71500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>45400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>430800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>71500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E83" s="3">
         <v>41200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4100</v>
       </c>
       <c r="N83" s="3">
         <v>4100</v>
       </c>
       <c r="O83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>817300</v>
+      </c>
+      <c r="E89" s="3">
         <v>210100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>806200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1107800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>376600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1123300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>393200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>135600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>386200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>372600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-262700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-133700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-151900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-214500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>158400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-2800</v>
       </c>
       <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-154800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-136400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-97200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-74300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-312800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-159700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>50200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-89500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-75800</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,57 +4887,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-298500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-393600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-628500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1202600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-604900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-377200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-219500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-76500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-117300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-103000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>309300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>337900</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4723,73 +4971,79 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-20500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21600</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9900</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>364100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-319900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>80500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-109700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>302200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>205500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-243600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>273700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>174000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-336000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>73000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>88600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>113900</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
